--- a/data_sources/Medicos.xlsx
+++ b/data_sources/Medicos.xlsx
@@ -455,21 +455,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pastor Segismundo Manso Andrés</t>
+          <t>Verónica Cabeza Quesada</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Neurología</t>
+          <t>Ginecología</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>45933.94700231482</v>
+        <v>45699.12445601852</v>
       </c>
     </row>
     <row r="3">
@@ -480,21 +480,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Matilde Herranz Millán</t>
+          <t>Pastora Salvà-Gutiérrez</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cardiología</t>
+          <t>Cirugía General</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46075.66068287037</v>
+        <v>45714.073125</v>
       </c>
     </row>
     <row r="4">
@@ -505,21 +505,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Virginia Ricarda Vilar Casares</t>
+          <t>Carla Naranjo Raya</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ginecología</t>
+          <t>Traumatología</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>45670.22179398148</v>
+        <v>45923.6778587963</v>
       </c>
     </row>
     <row r="5">
@@ -530,12 +530,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carolina Yaiza Calleja Aragonés</t>
+          <t>Ceferino del Cobos</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medicina General</t>
+          <t>Traumatología</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>45951.46836805555</v>
+        <v>46029.90452546296</v>
       </c>
     </row>
     <row r="6">
@@ -555,21 +555,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fausto Correa Abellán</t>
+          <t>Máximo Leon Giner</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pediatría</t>
+          <t>Cardiología</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Inactivo</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45683.40704861111</v>
+        <v>45894.29232638889</v>
       </c>
     </row>
     <row r="7">
@@ -580,12 +580,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Matilde Gomila-Morell</t>
+          <t>Fátima Sala Arnal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Traumatología</t>
+          <t>Ginecología</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46004.08299768518</v>
+        <v>45947.41186342593</v>
       </c>
     </row>
     <row r="8">
@@ -605,12 +605,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Julio Real Requena</t>
+          <t>Amparo Barrena-Padilla</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cardiología</t>
+          <t>Ginecología</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>45839.35488425926</v>
+        <v>45753.93578703704</v>
       </c>
     </row>
     <row r="9">
@@ -630,12 +630,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lara Higueras</t>
+          <t>Calixta Casado Alcalá</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CIRUGÍA GENERAL</t>
+          <t>Neurología</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="E9" s="1" t="n">
-        <v>45926.31206018518</v>
+        <v>45994.03592592593</v>
       </c>
     </row>
     <row r="10">
@@ -655,12 +655,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Teodosio Navarro-Querol</t>
+          <t>Severiano Barco</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cardiología</t>
+          <t>Traumatología</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>45755.95109953704</v>
+        <v>46039.0574537037</v>
       </c>
     </row>
     <row r="11">
@@ -680,12 +680,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Purificación de Puerta</t>
+          <t>Teobaldo Iniesta Alegre</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cardiología</t>
+          <t>Neurología</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>45940.86471064815</v>
+        <v>45795.66302083333</v>
       </c>
     </row>
     <row r="12">
@@ -705,12 +705,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fernanda Badía Cañas</t>
+          <t>Pascual Roig Balaguer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>neurología</t>
+          <t>Pediatría</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="E12" s="1" t="n">
-        <v>45916.3581712963</v>
+        <v>46103.42813657408</v>
       </c>
     </row>
     <row r="13">
@@ -730,12 +730,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Camila Jimena Buendía Vega</t>
+          <t>Juan Pedro</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ginecología</t>
+          <t>Traumatología</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="E13" s="1" t="n">
-        <v>45804.69284722222</v>
+        <v>45944.9247337963</v>
       </c>
     </row>
     <row r="14">
@@ -755,12 +755,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nayara Guzman Mate</t>
+          <t>Sara Luna-Herrera</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ginecología</t>
+          <t>Medicina General</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46065.04149305556</v>
+        <v>45716.16670138889</v>
       </c>
     </row>
     <row r="15">
@@ -780,12 +780,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Anselma Benítez</t>
+          <t>Jafet Poza Espejo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Neurología</t>
+          <t>Pediatría</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46003.45231481481</v>
+        <v>45980.52262731481</v>
       </c>
     </row>
     <row r="16">
@@ -805,21 +805,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Modesta Mármol</t>
+          <t>Victoria Lozano-Bertrán</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>medicina general</t>
+          <t>Traumatología</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46154.39585648148</v>
+        <v>46124.56787037037</v>
       </c>
     </row>
     <row r="17">
@@ -830,21 +830,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Samu Carvajal Arribas</t>
+          <t>Martin Cerdá Alcalde</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cirugía General</t>
+          <t>Neurología</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Inactivo</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46121.71195601852</v>
+        <v>45704.83174768519</v>
       </c>
     </row>
     <row r="18">
@@ -855,12 +855,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Charo García Cuevas</t>
+          <t>Trinidad Ferrer Giménez</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cirugía General</t>
+          <t>Neurología</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="E18" s="1" t="n">
-        <v>45968.69339120371</v>
+        <v>45669.92002314814</v>
       </c>
     </row>
     <row r="19">
@@ -880,21 +880,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nazaret Ochoa-Suárez</t>
+          <t>Sandalio Juan Pablo Guillén Tomás</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cirugía General</t>
+          <t>Pediatría</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Inactivo</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="E19" s="1" t="n">
-        <v>45918.34560185186</v>
+        <v>46075.42537037037</v>
       </c>
     </row>
     <row r="20">
@@ -905,12 +905,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rosario Jurado</t>
+          <t>Cándida Rosenda Ribas Benito</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>traumatología</t>
+          <t>Cirugía General</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="E20" s="1" t="n">
-        <v>45830.68143518519</v>
+        <v>45840.80373842592</v>
       </c>
     </row>
     <row r="21">
@@ -930,21 +930,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Emelina Encarnita Enríquez Chaparro</t>
+          <t>Maricela Quintanilla Amador</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Neurología</t>
+          <t>Pediatría</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46198.83039351852</v>
+        <v>45920.6519675926</v>
       </c>
     </row>
     <row r="22">
@@ -955,21 +955,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rodolfo de Jove</t>
+          <t>Florentina Gabaldón</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cirugía General</t>
+          <t>Medicina General</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="E22" s="1" t="n">
-        <v>45973.54165509259</v>
+        <v>45672.5024537037</v>
       </c>
     </row>
     <row r="23">
@@ -980,21 +980,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Elisa de Ochoa</t>
+          <t>Lupe Adán-Puga</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pediatría</t>
+          <t>Medicina General</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="E23" s="1" t="n">
-        <v>45850.97553240741</v>
+        <v>46102.19431712963</v>
       </c>
     </row>
     <row r="24">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Eusebio Carballo Bou</t>
+          <t>Guiomar Monreal Rosselló</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cardiología</t>
+          <t>Neurología</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="E24" s="1" t="n">
-        <v>45935.53096064815</v>
+        <v>45661.42824074074</v>
       </c>
     </row>
     <row r="25">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gustavo Baena</t>
+          <t>Ambrosio de Pareja</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46150.54856481482</v>
+        <v>45804.19472222222</v>
       </c>
     </row>
     <row r="26">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lupe de Solera</t>
+          <t>Susana del Carvajal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="E26" s="1" t="n">
-        <v>45688.98228009259</v>
+        <v>45656.3934837963</v>
       </c>
     </row>
     <row r="27">
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jerónimo Cepeda Cazorla</t>
+          <t>Jesús Arnau</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ginecología</t>
+          <t>Medicina General</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46076.94759259259</v>
+        <v>45868.10899305555</v>
       </c>
     </row>
     <row r="28">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Eloy Pineda Godoy</t>
+          <t>Emigdio del Piquer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pediatría</t>
+          <t>Cardiología</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="E28" s="1" t="n">
-        <v>45856.15248842593</v>
+        <v>45926.25784722222</v>
       </c>
     </row>
     <row r="29">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aureliano Raya Lerma</t>
+          <t>Omar Escolano Rocha</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="E29" s="1" t="n">
-        <v>45985.41304398148</v>
+        <v>45999.24394675926</v>
       </c>
     </row>
     <row r="30">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Raimundo Luján-Sanz</t>
+          <t>Nilo Campos Blanes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Traumatología</t>
+          <t>Pediatría</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="E30" s="1" t="n">
-        <v>45953.77043981481</v>
+        <v>45925.05017361111</v>
       </c>
     </row>
     <row r="31">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Olimpia Quintana Sandoval</t>
+          <t>Hortensia Aparicio Aragonés</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cirugía General</t>
+          <t>pediatría</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="E31" s="1" t="n">
-        <v>45819.59061342593</v>
+        <v>45751.61820601852</v>
       </c>
     </row>
     <row r="32">
@@ -1205,21 +1205,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Merche Pérez Lobato</t>
+          <t>Plinio Barrera Macias</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pediatría</t>
+          <t>Neurología</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Inactivo</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46036.86949074074</v>
+        <v>45741.98456018518</v>
       </c>
     </row>
     <row r="33">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Heriberto Nicolás Cáceres Peral</t>
+          <t>Esther Manzanares Valcárcel</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Traumatología</t>
+          <t>Cirugía General</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="E33" s="1" t="n">
-        <v>45825.97150462963</v>
+        <v>46003.03135416667</v>
       </c>
     </row>
     <row r="34">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aníbal Calleja Olmedo</t>
+          <t>Consuela Vendrell Padilla</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cirugía General</t>
+          <t>Medicina General</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="E34" s="1" t="n">
-        <v>45740.14461805556</v>
+        <v>45951.13548611111</v>
       </c>
     </row>
     <row r="35">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Norberto Barberá Bou</t>
+          <t>Primitiva Robledo Donaire</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Inactivo</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="E35" s="1" t="n">
-        <v>45953.81622685185</v>
+        <v>45797.77002314815</v>
       </c>
     </row>
     <row r="36">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Anna Prieto-Perales</t>
+          <t>Rafa Coll</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46100.69883101852</v>
+        <v>45881.81681712963</v>
       </c>
     </row>
     <row r="37">
@@ -1330,21 +1330,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Teodosio Castelló Leon</t>
+          <t>Trinidad Raya-Barceló</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Traumatología</t>
+          <t>ginecología</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46151.43398148148</v>
+        <v>45707.506875</v>
       </c>
     </row>
     <row r="38">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ester Falcó-Puga</t>
+          <t>Ignacio Rico Codina Diez</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Traumatología</t>
+          <t>Pediatría</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>45727.79670138889</v>
+        <v>46123.31788194444</v>
       </c>
     </row>
     <row r="39">
@@ -1380,21 +1380,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Agustina Vaquero-Bastida</t>
+          <t>Gregorio del Ramis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Medicina General</t>
+          <t>Cirugía General</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46042.84695601852</v>
+        <v>45733.73344907408</v>
       </c>
     </row>
     <row r="40">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Edgardo Alberola Egea</t>
+          <t>Cristina Vallejo-Exposito</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pediatría</t>
+          <t>PEDIATRÍA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="E40" s="1" t="n">
-        <v>45932.69636574074</v>
+        <v>46123.57280092593</v>
       </c>
     </row>
     <row r="41">
@@ -1430,21 +1430,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Esperanza Angelita Bosch Anguita</t>
+          <t>Amando Bayo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cardiología</t>
+          <t>Neurología</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="E41" s="1" t="n">
-        <v>45748.4025</v>
+        <v>45934.57931712963</v>
       </c>
     </row>
     <row r="42">
@@ -1455,21 +1455,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Luna del Barba</t>
+          <t>José Mari Cifuentes Otero</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cirugía General</t>
+          <t>Ginecología</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="E42" s="1" t="n">
-        <v>45691.32119212963</v>
+        <v>45744.81773148148</v>
       </c>
     </row>
     <row r="43">
@@ -1480,21 +1480,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Leticia Cerdá Querol</t>
+          <t>Pili Checa-Iglesias</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ginecología</t>
+          <t>Neurología</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Inactivo</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="E43" s="1" t="n">
-        <v>45760.97820601852</v>
+        <v>46133.22789351852</v>
       </c>
     </row>
     <row r="44">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Noé Seco Cañas</t>
+          <t>María Guillen Ferrera</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Medicina General</t>
+          <t>Cirugía General</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="E44" s="1" t="n">
-        <v>45721.42274305555</v>
+        <v>45850.57527777777</v>
       </c>
     </row>
     <row r="45">
@@ -1530,21 +1530,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mamen Bermudez Mena</t>
+          <t>Marc Blazquez Alberdi</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MEDICINA GENERAL</t>
+          <t>Ginecología</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="E45" s="1" t="n">
-        <v>45714.5862037037</v>
+        <v>45717.83232638889</v>
       </c>
     </row>
     <row r="46">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Josefa Arroyo Ariño</t>
+          <t>Julie Palacio Arjona</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>traumatología</t>
+          <t>Medicina General</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="E46" s="1" t="n">
-        <v>45764.8181712963</v>
+        <v>46042.21825231481</v>
       </c>
     </row>
     <row r="47">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cristian Flores-Laguna</t>
+          <t>Domitila Aura Roma Pardo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pediatría</t>
+          <t>Traumatología</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46152.65585648148</v>
+        <v>45922.77489583333</v>
       </c>
     </row>
     <row r="48">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fortunata Rosselló Valenzuela</t>
+          <t>Dalila Torrent Pérez</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cirugía General</t>
+          <t>Medicina General</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="E48" s="1" t="n">
-        <v>45666.78253472222</v>
+        <v>45749.53835648148</v>
       </c>
     </row>
     <row r="49">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Valentina Lago Tamarit</t>
+          <t>Loida Raya Verdugo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Medicina General</t>
+          <t>Neurología</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46139.20662037037</v>
+        <v>46012.52233796296</v>
       </c>
     </row>
     <row r="50">
@@ -1655,21 +1655,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Amarilis Nuria Lastra Guzman</t>
+          <t>Fernanda Portillo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pediatría</t>
+          <t>Ginecología</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Inactivo</t>
+          <t>Activo</t>
         </is>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46171.28665509259</v>
+        <v>45733.93015046296</v>
       </c>
     </row>
     <row r="51">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rolando Valencia Seco</t>
+          <t>Eduardo Pou Roura</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Traumatología</t>
+          <t>Medicina General</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46169.67591435185</v>
+        <v>46075.8608912037</v>
       </c>
     </row>
   </sheetData>
